--- a/htr-strucGenerale-CDA/ig/StructureDefinition-Patient.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-Patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T10:35:11+00:00</t>
+    <t>2025-04-18T14:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -234,10 +234,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>*</t>
+    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -247,10 +244,13 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>Patient.identifiantPatient</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -292,19 +292,19 @@
     <t>Eléments permettant de décrire l’identité du patient/usager, son sexe, sa date et son lieu de naissance, son (ses) représentant(s), etc...</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient</t>
   </si>
   <si>
     <t>Noms et prénoms du patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.noms</t>
-  </si>
-  <si>
-    <t>Noms du patient/usager.</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenoms.noms.nomNaissance</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.nom</t>
+  </si>
+  <si>
+    <t>Nom du patient/usager.</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.nom.nomNaissance</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -315,111 +315,31 @@
       - Obligatoire si le matricule INS est présent.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.noms.nomUtilise</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.nom.nomUtilise</t>
   </si>
   <si>
     <t>Nom utilisé du patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Prénoms du patient/usager.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.listePrenoms</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom</t>
+  </si>
+  <si>
+    <t>Prénom du patient/usager.</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.listePrenoms</t>
   </si>
   <si>
     <t>Liste des prénoms de l'acte de naissance.Obligatoire si le matricule INS est présent.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.premierPrenom</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.premierPrenom</t>
   </si>
   <si>
     <t>Premier prénom de l'acte de naissance.Obligatoire si le matricule INS est présent</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.prenomUtilise</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.prenomUtilise</t>
   </si>
   <si>
     <t>Prénom utilisé.</t>
@@ -479,15 +399,6 @@
     <t>Représentant du patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.representantPatient.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.extension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.modifierExtension</t>
-  </si>
-  <si>
     <t>Patient.personnePhysique.representantPatient.adresse</t>
   </si>
   <si>
@@ -506,31 +417,13 @@
     <t>Personne représentant le patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.extension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms</t>
+    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient</t>
   </si>
   <si>
     <t>Noms et Prénoms du représentant.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.extension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.modifierExtension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.nom</t>
+    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.nom</t>
   </si>
   <si>
     <t>3</t>
@@ -539,7 +432,7 @@
     <t>Nom du représentant.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.prenom</t>
+    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.prenom</t>
   </si>
   <si>
     <t>Prénom du représentant.</t>
@@ -551,164 +444,13 @@
     <t>Structure représentant le patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.extension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.modifierExtension</t>
-  </si>
-  <si>
     <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant</t>
   </si>
   <si>
     <t>Identifiant de la structure.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.extension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.type</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant.nom</t>
+    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.nom</t>
   </si>
   <si>
     <t>Nom de la structure.</t>
@@ -722,28 +464,19 @@
   - Le lieu de naissance est constitué du nom et/ou de l’adresse du lieu de naissance du patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.lieuNaissance.id</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.lieuNaissance.extension</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.lieuNaissance.modifierExtension</t>
-  </si>
-  <si>
     <t>Patient.personnePhysique.lieuNaissance.nomLieuNaissance</t>
   </si>
   <si>
     <t>Nom du lieu de naissance du patient/usager.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.lieuNaissance.adresseEtCodeOfficielGeographique</t>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance</t>
   </si>
   <si>
     <t>Adresse et code officiel géographique du lieu de naissance.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.lieuNaissance.CodeOfficielGeographique</t>
+    <t>Patient.personnePhysique.lieuNaissance.CodeOfficielGeographiqueLieuNaissance</t>
   </si>
   <si>
     <t>Code Officiel Géographique (COG) de la commune ou du pays du lieu de naissance.
@@ -1049,41 +782,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="88.08203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="88.08203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="96.12109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="96.12109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="79.93359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="96.12109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1215,19 +948,19 @@
         <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1284,13 +1017,13 @@
         <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>72</v>
@@ -1301,10 +1034,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1312,10 +1045,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>72</v>
@@ -1384,13 +1117,13 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH3" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>72</v>
@@ -1412,10 +1145,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1487,10 +1220,10 @@
         <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1512,10 +1245,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1587,10 +1320,10 @@
         <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
@@ -1612,10 +1345,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1687,10 +1420,10 @@
         <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>72</v>
@@ -1712,10 +1445,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1787,10 +1520,10 @@
         <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>72</v>
@@ -1812,10 +1545,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
@@ -1887,10 +1620,10 @@
         <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
@@ -1912,10 +1645,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>72</v>
@@ -1987,10 +1720,10 @@
         <v>94</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>72</v>
@@ -2012,10 +1745,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
@@ -2087,10 +1820,10 @@
         <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
@@ -2112,10 +1845,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -2127,13 +1860,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2187,24 +1920,24 @@
         <v>99</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2212,10 +1945,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
@@ -2230,10 +1963,10 @@
         <v>95</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2284,13 +2017,13 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
@@ -2301,21 +2034,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2327,17 +2060,15 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
@@ -2374,75 +2105,71 @@
         <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>72</v>
       </c>
@@ -2490,27 +2217,27 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2521,7 +2248,7 @@
         <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2533,13 +2260,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2590,13 +2317,13 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
@@ -2607,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2621,7 +2348,7 @@
         <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2633,13 +2360,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2690,13 +2417,13 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
@@ -2707,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2718,10 +2445,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
@@ -2733,13 +2460,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2790,13 +2517,13 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>72</v>
@@ -2807,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2818,10 +2545,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -2833,13 +2560,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2890,13 +2617,13 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
@@ -2907,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2918,10 +2645,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
@@ -2933,13 +2660,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2990,13 +2717,13 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
@@ -3007,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3018,10 +2745,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
@@ -3033,13 +2760,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3090,13 +2817,13 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>72</v>
@@ -3107,10 +2834,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3118,10 +2845,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>72</v>
@@ -3133,13 +2860,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3190,13 +2917,13 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>72</v>
@@ -3207,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3218,10 +2945,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>72</v>
@@ -3233,13 +2960,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3290,13 +3017,13 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>72</v>
@@ -3307,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3318,10 +3045,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
@@ -3333,13 +3060,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3390,13 +3117,13 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>72</v>
@@ -3407,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3418,10 +3145,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>72</v>
@@ -3433,13 +3160,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3490,27 +3217,27 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3521,7 +3248,7 @@
         <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>72</v>
@@ -3533,13 +3260,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3590,13 +3317,13 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>72</v>
@@ -3607,21 +3334,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -3633,17 +3360,15 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>72</v>
@@ -3680,75 +3405,71 @@
         <v>72</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>72</v>
       </c>
@@ -3796,27 +3517,27 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3824,10 +3545,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>72</v>
@@ -3839,13 +3560,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3896,13 +3617,13 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>72</v>
@@ -3913,10 +3634,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3924,10 +3645,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>72</v>
@@ -3939,13 +3660,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3996,13 +3717,13 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>72</v>
@@ -4013,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4024,10 +3745,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>72</v>
@@ -4039,13 +3760,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4096,27 +3817,27 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4124,10 +3845,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>72</v>
@@ -4139,13 +3860,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4196,13 +3917,13 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>72</v>
@@ -4213,21 +3934,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>72</v>
@@ -4239,17 +3960,15 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>72</v>
@@ -4286,75 +4005,71 @@
         <v>72</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>72</v>
       </c>
@@ -4402,27 +4117,27 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4430,10 +4145,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4445,13 +4160,13 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4502,2654 +4217,18 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="P37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/htr-strucGenerale-CDA/ig/StructureDefinition-Patient.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T14:53:38+00:00</t>
+    <t>2025-04-22T14:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
